--- a/data/trans_bre/IMC_inf_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,5; -1,07</t>
+          <t>-31,84; -0,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 8,92</t>
+          <t>-29,81; 8,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 10,58</t>
+          <t>-28,44; 10,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 19,29</t>
+          <t>-13,7; 18,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,06; -1,81</t>
+          <t>-63,25; -0,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 23,38</t>
+          <t>-54,15; 23,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 26,63</t>
+          <t>-44,93; 23,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 114,56</t>
+          <t>-42,77; 102,97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -1,04</t>
+          <t>-23,8; 0,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 5,79</t>
+          <t>-19,31; 6,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,55; -1,25</t>
+          <t>-26,54; -1,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,23; -4,36</t>
+          <t>-38,13; -3,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,86; -2,14</t>
+          <t>-44,76; 1,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 15,13</t>
+          <t>-36,09; 15,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,38; -2,54</t>
+          <t>-43,56; -3,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,83; -12,52</t>
+          <t>-73,27; -10,05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,94; -5,13</t>
+          <t>-30,28; -4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 17,22</t>
+          <t>-13,76; 16,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 5,38</t>
+          <t>-23,72; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,77; -7,23</t>
+          <t>-36,57; -8,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -14,41</t>
+          <t>-67,17; -12,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 39,67</t>
+          <t>-24,94; 37,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 17,77</t>
+          <t>-53,97; 21,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -15,74</t>
+          <t>-62,68; -19,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 16,11</t>
+          <t>-11,32; 14,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,31; -7,44</t>
+          <t>-38,29; -8,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 4,42</t>
+          <t>-27,53; 4,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 17,46</t>
+          <t>-22,03; 19,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 52,2</t>
+          <t>-24,75; 43,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,45; -15,5</t>
+          <t>-63,01; -16,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 11,01</t>
+          <t>-48,73; 10,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,11; 95,66</t>
+          <t>-51,3; 110,24</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 9,44</t>
+          <t>-26,68; 9,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 6,6</t>
+          <t>-35,15; 6,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 16,06</t>
+          <t>-21,04; 18,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 7,0</t>
+          <t>-28,52; 4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 17,52</t>
+          <t>-39,54; 17,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 19,58</t>
+          <t>-62,07; 21,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 65,07</t>
+          <t>-47,82; 75,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 17,68</t>
+          <t>-52,31; 10,77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,13; -10,21</t>
+          <t>-40,12; -10,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 26,05</t>
+          <t>-8,52; 26,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,81; -2,71</t>
+          <t>-35,23; -1,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 5,44</t>
+          <t>-26,63; 3,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,04; -23,14</t>
+          <t>-70,32; -22,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 103,01</t>
+          <t>-18,66; 97,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,55; -3,95</t>
+          <t>-63,04; -3,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 27,15</t>
+          <t>-60,67; 14,88</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 0,05</t>
+          <t>-20,65; -0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,21; -3,65</t>
+          <t>-25,83; -4,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 3,95</t>
+          <t>-15,75; 4,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 4,22</t>
+          <t>-19,69; 5,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 0,15</t>
+          <t>-45,2; -0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -7,65</t>
+          <t>-42,75; -9,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-41,12; 13,28</t>
+          <t>-39,47; 15,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 12,17</t>
+          <t>-41,82; 14,39</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 8,22</t>
+          <t>-11,72; 8,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 4,48</t>
+          <t>-15,93; 4,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,41; -0,54</t>
+          <t>-20,13; -1,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,81; -1,68</t>
+          <t>-20,76; -0,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 19,34</t>
+          <t>-22,57; 20,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 8,42</t>
+          <t>-27,17; 7,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,46; -0,31</t>
+          <t>-39,16; -2,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,65; -4,81</t>
+          <t>-50,06; 0,22</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -5,16</t>
+          <t>-14,62; -5,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -3,98</t>
+          <t>-13,62; -3,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -5,35</t>
+          <t>-14,63; -4,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -5,18</t>
+          <t>-15,83; -4,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,69; -11,96</t>
+          <t>-30,91; -13,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -8,09</t>
+          <t>-25,56; -6,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -12,61</t>
+          <t>-31,25; -11,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -15,25</t>
+          <t>-38,97; -13,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,84; -0,78</t>
+          <t>-33,17; -1,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 8,01</t>
+          <t>-29,3; 7,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 10,21</t>
+          <t>-27,77; 8,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 18,53</t>
+          <t>-13,37; 18,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,25; -0,84</t>
+          <t>-63,91; -4,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 23,02</t>
+          <t>-54,76; 21,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 23,66</t>
+          <t>-45,12; 19,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 102,97</t>
+          <t>-43,01; 110,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 0,45</t>
+          <t>-25,79; -1,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 6,08</t>
+          <t>-19,7; 7,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,54; -1,97</t>
+          <t>-26,16; -1,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,13; -3,7</t>
+          <t>-37,73; -3,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 1,05</t>
+          <t>-47,21; -2,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 15,9</t>
+          <t>-37,87; 18,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -3,91</t>
+          <t>-43,91; -3,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,27; -10,05</t>
+          <t>-73,1; -12,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,28; -4,56</t>
+          <t>-30,34; -5,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 16,19</t>
+          <t>-15,07; 16,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 5,9</t>
+          <t>-22,75; 4,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,57; -8,74</t>
+          <t>-36,21; -7,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,17; -12,43</t>
+          <t>-65,81; -14,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 37,7</t>
+          <t>-26,73; 40,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 21,67</t>
+          <t>-52,82; 16,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,68; -19,38</t>
+          <t>-63,0; -16,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 14,33</t>
+          <t>-10,9; 14,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,29; -8,21</t>
+          <t>-38,5; -8,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 4,72</t>
+          <t>-25,63; 5,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 19,44</t>
+          <t>-21,56; 20,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 43,82</t>
+          <t>-25,11; 46,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,01; -16,21</t>
+          <t>-63,72; -16,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 10,4</t>
+          <t>-47,22; 14,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 110,24</t>
+          <t>-51,66; 120,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 9,3</t>
+          <t>-26,9; 9,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 6,85</t>
+          <t>-37,56; 6,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 18,2</t>
+          <t>-19,36; 16,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 4,66</t>
+          <t>-28,47; 5,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 17,84</t>
+          <t>-39,86; 17,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,07; 21,62</t>
+          <t>-64,78; 18,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 75,8</t>
+          <t>-45,15; 70,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 10,77</t>
+          <t>-52,62; 14,09</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,12; -10,32</t>
+          <t>-39,72; -11,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 26,07</t>
+          <t>-9,67; 24,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,23; -1,38</t>
+          <t>-34,33; -1,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 3,64</t>
+          <t>-26,61; 3,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -22,42</t>
+          <t>-69,19; -25,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 97,22</t>
+          <t>-22,09; 89,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,04; -3,76</t>
+          <t>-60,25; -3,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 14,88</t>
+          <t>-61,47; 14,84</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,65; -0,26</t>
+          <t>-20,32; -0,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -4,84</t>
+          <t>-25,72; -3,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 4,31</t>
+          <t>-15,67; 4,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 5,17</t>
+          <t>-19,69; 4,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,2; -0,4</t>
+          <t>-45,8; -2,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,75; -9,35</t>
+          <t>-42,64; -7,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 15,24</t>
+          <t>-39,07; 15,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 14,39</t>
+          <t>-41,76; 13,05</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 8,66</t>
+          <t>-13,26; 7,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 4,09</t>
+          <t>-15,6; 5,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,13; -1,41</t>
+          <t>-20,64; -0,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -0,78</t>
+          <t>-20,42; -0,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 20,09</t>
+          <t>-25,0; 16,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 7,96</t>
+          <t>-25,35; 10,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,16; -2,93</t>
+          <t>-39,44; -1,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 0,22</t>
+          <t>-50,17; -3,0</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -5,7</t>
+          <t>-14,45; -5,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -3,32</t>
+          <t>-13,6; -3,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -4,48</t>
+          <t>-14,87; -5,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,83; -4,76</t>
+          <t>-16,53; -5,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,91; -13,46</t>
+          <t>-30,44; -13,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,56; -6,95</t>
+          <t>-25,63; -6,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -11,01</t>
+          <t>-31,9; -12,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -13,84</t>
+          <t>-40,01; -13,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,17; -1,93</t>
+          <t>-31,5; -1,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 7,13</t>
+          <t>-28,9; 8,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 8,29</t>
+          <t>-27,48; 10,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 18,96</t>
+          <t>-11,63; 16,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,91; -4,48</t>
+          <t>-62,06; -1,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 21,28</t>
+          <t>-52,51; 23,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 19,64</t>
+          <t>-43,27; 26,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 110,38</t>
+          <t>-39,74; 95,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-18,59</t>
+          <t>-13,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-41,23%</t>
+          <t>-31,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,79; -1,1</t>
+          <t>-25,31; -1,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 7,55</t>
+          <t>-20,56; 5,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,16; -1,68</t>
+          <t>-24,55; -1,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,73; -3,66</t>
+          <t>-28,0; -1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,21; -2,41</t>
+          <t>-46,86; -2,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 18,41</t>
+          <t>-38,63; 15,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,91; -3,88</t>
+          <t>-41,38; -2,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,1; -12,39</t>
+          <t>-53,61; -2,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-22,48</t>
+          <t>-22,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-44,27%</t>
+          <t>-44,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -5,66</t>
+          <t>-31,94; -5,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 16,56</t>
+          <t>-14,89; 17,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 4,72</t>
+          <t>-23,63; 5,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,21; -7,86</t>
+          <t>-36,91; -7,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,81; -14,89</t>
+          <t>-69,08; -14,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 40,76</t>
+          <t>-26,03; 39,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,82; 16,94</t>
+          <t>-53,05; 17,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,0; -16,27</t>
+          <t>-63,64; -16,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-4,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,67%</t>
+          <t>-13,56%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 14,93</t>
+          <t>-11,37; 16,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,5; -8,07</t>
+          <t>-38,31; -7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 5,89</t>
+          <t>-26,46; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 20,88</t>
+          <t>-24,18; 15,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 46,18</t>
+          <t>-24,94; 52,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,72; -16,3</t>
+          <t>-63,45; -15,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 14,93</t>
+          <t>-47,12; 11,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 120,4</t>
+          <t>-57,46; 81,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,92</t>
+          <t>-13,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-23,78%</t>
+          <t>-28,6%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 9,13</t>
+          <t>-26,75; 9,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 6,87</t>
+          <t>-36,61; 6,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 16,98</t>
+          <t>-18,99; 16,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 5,16</t>
+          <t>-30,31; 2,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 17,91</t>
+          <t>-39,06; 17,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 18,98</t>
+          <t>-66,15; 19,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 70,98</t>
+          <t>-44,09; 65,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 14,09</t>
+          <t>-55,32; 7,57</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-11,36</t>
+          <t>-10,92</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-31,08%</t>
+          <t>-30,57%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,72; -11,41</t>
+          <t>-40,13; -10,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 24,69</t>
+          <t>-6,56; 26,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,33; -1,83</t>
+          <t>-35,81; -2,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 3,57</t>
+          <t>-26,19; 5,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,19; -25,34</t>
+          <t>-70,04; -23,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 89,46</t>
+          <t>-14,09; 103,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,25; -3,19</t>
+          <t>-61,55; -3,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 14,84</t>
+          <t>-59,85; 28,11</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-9,58</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-18,68%</t>
+          <t>-22,48%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -0,78</t>
+          <t>-19,72; 0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,72; -3,66</t>
+          <t>-24,21; -3,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 4,66</t>
+          <t>-16,53; 3,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 4,56</t>
+          <t>-21,65; 1,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,8; -2,58</t>
+          <t>-43,27; 0,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,64; -7,08</t>
+          <t>-41,76; -7,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 15,61</t>
+          <t>-41,12; 13,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,76; 13,05</t>
+          <t>-43,35; 4,79</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-10,84</t>
+          <t>-11,69</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-29,92%</t>
+          <t>-32,55%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 7,27</t>
+          <t>-12,29; 8,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 5,17</t>
+          <t>-15,58; 4,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,64; -0,62</t>
+          <t>-20,41; -0,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -0,91</t>
+          <t>-22,85; -2,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 16,48</t>
+          <t>-23,24; 19,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 10,57</t>
+          <t>-26,71; 8,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,44; -1,33</t>
+          <t>-39,46; -0,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,17; -3,0</t>
+          <t>-54,1; -6,91</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,67</t>
+          <t>-10,84</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-27,36%</t>
+          <t>-27,52%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -5,91</t>
+          <t>-14,42; -5,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -3,44</t>
+          <t>-13,5; -3,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -5,13</t>
+          <t>-14,65; -5,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,53; -5,1</t>
+          <t>-15,8; -5,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,44; -13,47</t>
+          <t>-30,69; -11,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -6,89</t>
+          <t>-25,27; -8,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,9; -12,12</t>
+          <t>-31,02; -12,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-40,01; -13,9</t>
+          <t>-37,33; -15,87</t>
         </is>
       </c>
     </row>
